--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6666666666666666</v>
+        <v>0.1300813008130081</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.1726618705035971</v>
       </c>
       <c r="D2">
-        <v>0.6</v>
+        <v>0.8778625954198473</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.1300813008130081</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="C2">
-        <v>0.1726618705035971</v>
+        <v>0.2214285714285714</v>
       </c>
       <c r="D2">
-        <v>0.8778625954198473</v>
+        <v>0.8195488721804511</v>
       </c>
       <c r="E2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
